--- a/Train_copy_매핑양식.xlsx
+++ b/Train_copy_매핑양식.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Train_copy 매핑" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="📋 사용법" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="사용법" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,62 +27,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001e1e2e"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <color rgb="00fab387"/>
+      <name val="Calibri"/>
+      <color rgb="00888888"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <color rgb="00585b70"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00cdd6f4"/>
+      <name val="Calibri"/>
+      <color rgb="001F1F1F"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00cba6f7"/>
+      <color rgb="001F1F1F"/>
       <sz val="13"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00a6e3a1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="006c7086"/>
+      <color rgb="001F1F1F"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <color rgb="00fab387"/>
+      <name val="Calibri"/>
+      <color rgb="00444444"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="0089b4fa"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00f9e2af"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -91,52 +74,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00a6e3a1"/>
+        <fgColor rgb="002F3136"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0089b4fa"/>
+        <fgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00cba6f7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f38ba8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00fab387"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f9e2af"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0094e2d5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00313244"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00181825"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001e1e2e"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,76 +98,46 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="0045475a"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="0045475a"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="0045475a"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="0045475a"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -587,218 +505,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Source 파일명</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Target - Train 1</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Target - Train 2</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Target - Train 3</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Target - Train 4</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>Target - Train 5</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Target - Train 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>[Source 폴더 경로]</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>[Train1 Target 폴더 경로]</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>[Train2 Target 폴더 경로]</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>[Train3 Target 폴더 경로]</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>[Train4 Target 폴더 경로]</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>[Train5 Target 폴더 경로]</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>[Train6 Target 폴더 경로]</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Train 1 - Target 파일명</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Train 2 - Target 파일명</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Train 3 - Target 파일명</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Train 4 - Target 파일명</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Train 5 - Target 파일명</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Train 6 - Target 파일명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source 폴더 경로</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Train 1 Target 폴더 경로</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Train 2 Target 폴더 경로</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Train 3 Target 폴더 경로</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Train 4 Target 폴더 경로</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Train 5 Target 폴더 경로</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Train 6 Target 폴더 경로</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>예) 22300-PID-10101.pdf</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>예) 22300-PID-10101_T1.pdf</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>예) 22300-PID-10101_T2.pdf</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>예) 22300-PID-10101_T3.pdf</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>예) 22300-PID-10101_T4.pdf</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>예) 22300-PID-10101_T5.pdf</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>예) 22300-PID-10101_T6.pdf</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n"/>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="11" t="n"/>
-      <c r="G5" s="11" t="n"/>
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -811,140 +692,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Train_copy 매핑 파일 사용법</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="19" customHeight="1">
-      <c r="A2" s="13" t="inlineStr"/>
-    </row>
-    <row r="3" ht="19" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>【시트: Train_copy 매핑】</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="19" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1행  헤더 (수정하지 마세요)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2행  각 열의 폴더 경로 입력  (경로에 \ 또는 / 포함 필수)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         예)  A2: C:\PID\Master     B2: C:\PID\Train1_Target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3행  예시 행 (삭제 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4행~  실제 파일명 입력  (.pdf 확장자 생략 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="13" t="inlineStr"/>
-    </row>
-    <row r="10" ht="19" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>【Source (A열)】</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A2: Source 폴더 경로   A4~: Source 파일명</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>【Target (B~G열 = Train 1~6)】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B2~G2: 각 Train의 Target 폴더 경로</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B4~G4: 해당 Train의 Target 파일명</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  파일 없는 Train은 해당 셀을 비워두세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>【실행 순서】</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Train_copy 실행 → Source 폴더 선택 (GUI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. 📂 Excel 매핑 버튼 클릭 → 이 파일 선택</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. 매핑 편집에서 내용 확인 → 🚀 실행</t>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>■ 1행 (헤더): 수정하지 마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>■ 2행 (회색): 각 열의 폴더 경로를 입력합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     예)  A2: C:\PID\Master</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           B2: C:\PID\Train1_Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           C2: C:\PID\Train2_Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>■ 3행~: 파일명을 입력합니다. (.pdf 생략 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     예)  A3: 22300-PID-10101.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           B3: 22300-PID-10101_T1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     * 파일 없는 Train은 해당 셀을 비워두세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>■ 실행 순서</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     1. Train_copy 실행 → Source 폴더 선택 (GUI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     2. [📂 Excel 매핑] 버튼 → 이 파일 선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     3. [매핑 편집] 에서 내용 확인 후 [🚀 실행]</t>
         </is>
       </c>
     </row>
